--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,6 +811,135 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122436026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56217</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ryabäcken 5, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>385905</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6231815</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rya</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Obeserverad Utter bland stenar vid bäck</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>122436026</v>
       </c>
       <c r="B3" t="n">
-        <v>56217</v>
+        <v>56222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -832,11 +832,6 @@
       <c r="E3" t="n">
         <v>100077</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lutra lutra</t>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>122436026</v>
       </c>
       <c r="B3" t="n">
-        <v>56222</v>
+        <v>56226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,6 +831,11 @@
       </c>
       <c r="E3" t="n">
         <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>122436026</v>
       </c>
       <c r="B3" t="n">
-        <v>56226</v>
+        <v>56227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120909918</v>
+        <v>122436026</v>
       </c>
       <c r="B2" t="n">
-        <v>58185</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100077</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,16 +708,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
@@ -736,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385758</v>
+        <v>385905</v>
       </c>
       <c r="R2" t="n">
-        <v>6231985</v>
+        <v>6231815</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,27 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Groda osäker art</t>
+          <t>Obeserverad Utter bland stenar vid bäck</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -814,19 +799,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122436026</v>
+        <v>123275898</v>
       </c>
       <c r="B3" t="n">
-        <v>56321</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -849,12 +829,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs av hona med unge/ungar</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -862,14 +850,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ryabäcken 5, Sk</t>
+          <t>Kungabäcken 1, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385905</v>
+        <v>385762</v>
       </c>
       <c r="R3" t="n">
-        <v>6231815</v>
+        <v>6231546</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +869,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Örkelljunga</t>
+          <t>Klippan</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -891,32 +879,32 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Rya</t>
+          <t>Östra Ljungby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2018-08-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2018-08-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Obeserverad Utter bland stenar vid bäck</t>
+          <t>Utter med två ungar filmade i Kungabäcken vid bron.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,6 +928,526 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110877083</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kungamossen, Stidsvig, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>385637</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6232142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rya</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gröngöling observerad</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Hansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Hansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120909918</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ryabäcken 5, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>385758</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6231985</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rya</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Groda osäker art</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125997670</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ryabäcken 8, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>385893</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6231952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rya</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Småvänderot i bäck</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125997712</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ryabäcken 10, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>385855</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6231826</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örkelljunga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rya</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Småvänderot i bäck</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Mattsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4112-2025 artfynd.xlsx
+++ b/artfynd/A 4112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122436026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123275898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1056,6 +1071,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110877083</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1190,6 +1210,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120909918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1319,6 +1344,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125997670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1448,8 +1478,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125997712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>